--- a/Excel/Assignment/Assignment 1.xlsx
+++ b/Excel/Assignment/Assignment 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1a2133a404dad2f5/Desktop/Data Analist/Excel/Assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{6803DF09-001D-4DF1-B0FB-00915B7BF862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D2D7033-5F55-477F-A4BE-51F5F6B9F92B}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{6803DF09-001D-4DF1-B0FB-00915B7BF862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECF45E42-79DE-468C-A097-B68431AC8DE3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{D60FA03F-7E0B-4139-AFC0-C56A959624EC}"/>
   </bookViews>
@@ -106,8 +106,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="[$-409]dd\-mmm\-yy;@"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -155,12 +155,12 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -8319,6 +8319,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E2:E268">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
     <cfRule type="dataBar" priority="3">
       <dataBar>
@@ -8331,11 +8336,6 @@
           <x14:id>{E047F1FD-BC99-44AE-A19D-24AC4092613D}</x14:id>
         </ext>
       </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E268">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
-      <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
@@ -8351,8 +8351,9 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
